--- a/Results/Phase 2/Methanol/methanol photochemical ozone formation results.xlsx
+++ b/Results/Phase 2/Methanol/methanol photochemical ozone formation results.xlsx
@@ -3314,85 +3314,85 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.002305967191773194</v>
+        <v>0.002227618374706884</v>
       </c>
       <c r="C33" t="n">
-        <v>0.002157621528121197</v>
+        <v>0.002135200493149293</v>
       </c>
       <c r="D33" t="n">
-        <v>0.00230885866729617</v>
+        <v>0.002223465990599676</v>
       </c>
       <c r="E33" t="n">
-        <v>0.002034776221183427</v>
+        <v>0.002002634435666716</v>
       </c>
       <c r="F33" t="n">
-        <v>0.002254735637512488</v>
+        <v>0.002191134306460983</v>
       </c>
       <c r="G33" t="n">
-        <v>0.002288403592163735</v>
+        <v>0.002215748984993173</v>
       </c>
       <c r="H33" t="n">
-        <v>0.002432444693902413</v>
+        <v>0.002292226840510979</v>
       </c>
       <c r="I33" t="n">
-        <v>0.002334118244472987</v>
+        <v>0.002237546128416778</v>
       </c>
       <c r="J33" t="n">
-        <v>0.002316699779755952</v>
+        <v>0.002230815644354774</v>
       </c>
       <c r="K33" t="n">
-        <v>0.002494163573015236</v>
+        <v>0.002332067797524151</v>
       </c>
       <c r="L33" t="n">
-        <v>0.0023241939712412</v>
+        <v>0.002235281178487279</v>
       </c>
       <c r="M33" t="n">
-        <v>0.002740564027817243</v>
+        <v>0.002472949287809521</v>
       </c>
       <c r="N33" t="n">
-        <v>0.002383273077157957</v>
+        <v>0.002268705304795294</v>
       </c>
       <c r="O33" t="n">
-        <v>0.003572918534485229</v>
+        <v>0.003499466793724409</v>
       </c>
       <c r="P33" t="n">
-        <v>0.002255730879108576</v>
+        <v>0.002196383316835689</v>
       </c>
       <c r="Q33" t="n">
-        <v>0.002247035423848705</v>
+        <v>0.002188179494379318</v>
       </c>
       <c r="R33" t="n">
-        <v>0.002327946964000282</v>
+        <v>0.002233290380736681</v>
       </c>
       <c r="S33" t="n">
-        <v>0.002292040473144857</v>
+        <v>0.002217793768779192</v>
       </c>
       <c r="T33" t="n">
-        <v>0.002408862392924888</v>
+        <v>0.002281390572708896</v>
       </c>
       <c r="U33" t="n">
-        <v>0.005454638140239228</v>
+        <v>0.005327609013870909</v>
       </c>
       <c r="V33" t="n">
-        <v>0.002223308882112805</v>
+        <v>0.002176755038516252</v>
       </c>
       <c r="W33" t="n">
-        <v>0.005775550209545406</v>
+        <v>0.005658897724143257</v>
       </c>
       <c r="X33" t="n">
-        <v>0.002263596187973459</v>
+        <v>0.002197597957636859</v>
       </c>
       <c r="Y33" t="n">
-        <v>0.002308808939403689</v>
+        <v>0.002225668466148015</v>
       </c>
       <c r="Z33" t="n">
-        <v>0.004282066514063706</v>
+        <v>0.004226234011333864</v>
       </c>
       <c r="AA33" t="n">
-        <v>0.002397367142213422</v>
+        <v>0.002277807107162967</v>
       </c>
       <c r="AB33" t="n">
-        <v>0.002466342564744478</v>
+        <v>0.002311456426938207</v>
       </c>
     </row>
   </sheetData>
@@ -6286,85 +6286,85 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.0020723718686599</v>
+        <v>0.00206588581850589</v>
       </c>
       <c r="C33" t="n">
-        <v>0.002029698972728648</v>
+        <v>0.002018255387362446</v>
       </c>
       <c r="D33" t="n">
-        <v>0.00209082809144199</v>
+        <v>0.002076526274348402</v>
       </c>
       <c r="E33" t="n">
-        <v>0.001944451026885478</v>
+        <v>0.001935664659603146</v>
       </c>
       <c r="F33" t="n">
-        <v>0.002091808133326726</v>
+        <v>0.002076963192127451</v>
       </c>
       <c r="G33" t="n">
-        <v>0.002096544603322451</v>
+        <v>0.002080881734720262</v>
       </c>
       <c r="H33" t="n">
-        <v>0.002129596288782329</v>
+        <v>0.002098439846654392</v>
       </c>
       <c r="I33" t="n">
-        <v>0.002108422721302061</v>
+        <v>0.002086655824511813</v>
       </c>
       <c r="J33" t="n">
-        <v>0.00211093338414533</v>
+        <v>0.002089101115489627</v>
       </c>
       <c r="K33" t="n">
-        <v>0.00212828543339182</v>
+        <v>0.002099940331958791</v>
       </c>
       <c r="L33" t="n">
-        <v>0.00211004316697831</v>
+        <v>0.00208895150228986</v>
       </c>
       <c r="M33" t="n">
-        <v>0.002093809489862144</v>
+        <v>0.002078138989793065</v>
       </c>
       <c r="N33" t="n">
-        <v>0.002107354597169451</v>
+        <v>0.002086218059102968</v>
       </c>
       <c r="O33" t="n">
-        <v>0.003297241105380905</v>
+        <v>0.003274795937152448</v>
       </c>
       <c r="P33" t="n">
-        <v>0.002105161490716064</v>
+        <v>0.002086267782206866</v>
       </c>
       <c r="Q33" t="n">
-        <v>0.002086323632277055</v>
+        <v>0.002074101263513511</v>
       </c>
       <c r="R33" t="n">
-        <v>0.002123730827208263</v>
+        <v>0.002095234895230512</v>
       </c>
       <c r="S33" t="n">
-        <v>0.002107786514815714</v>
+        <v>0.002087810150971873</v>
       </c>
       <c r="T33" t="n">
-        <v>0.002116431510539954</v>
+        <v>0.002091281934215061</v>
       </c>
       <c r="U33" t="n">
-        <v>0.004913087279171645</v>
+        <v>0.004894050593112615</v>
       </c>
       <c r="V33" t="n">
-        <v>0.002114658421004124</v>
+        <v>0.002092059866512518</v>
       </c>
       <c r="W33" t="n">
-        <v>0.005420419476505197</v>
+        <v>0.005349648351137688</v>
       </c>
       <c r="X33" t="n">
-        <v>0.002294549435328749</v>
+        <v>0.002199028065635415</v>
       </c>
       <c r="Y33" t="n">
-        <v>0.002203409223211518</v>
+        <v>0.00214307534681425</v>
       </c>
       <c r="Z33" t="n">
-        <v>0.004115880997996346</v>
+        <v>0.004095373869374771</v>
       </c>
       <c r="AA33" t="n">
-        <v>0.00221275323516332</v>
+        <v>0.00214876809661609</v>
       </c>
       <c r="AB33" t="n">
-        <v>0.002084267467005058</v>
+        <v>0.002072244693243011</v>
       </c>
     </row>
   </sheetData>
@@ -9258,85 +9258,85 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.002253308745505641</v>
+        <v>0.002191065992078094</v>
       </c>
       <c r="C33" t="n">
-        <v>0.002142820260178675</v>
+        <v>0.002120659124190851</v>
       </c>
       <c r="D33" t="n">
-        <v>0.002270058013889762</v>
+        <v>0.002195982067611872</v>
       </c>
       <c r="E33" t="n">
-        <v>0.002021637760365231</v>
+        <v>0.001991818377627252</v>
       </c>
       <c r="F33" t="n">
-        <v>0.002188960857473105</v>
+        <v>0.002148655926518785</v>
       </c>
       <c r="G33" t="n">
-        <v>0.00226572003592151</v>
+        <v>0.002197728227573593</v>
       </c>
       <c r="H33" t="n">
-        <v>0.002341589984048948</v>
+        <v>0.002235436397312433</v>
       </c>
       <c r="I33" t="n">
-        <v>0.002272480171975243</v>
+        <v>0.002196905838816627</v>
       </c>
       <c r="J33" t="n">
-        <v>0.002294421440263536</v>
+        <v>0.002212800052012101</v>
       </c>
       <c r="K33" t="n">
-        <v>0.002409538421274134</v>
+        <v>0.002282578142116224</v>
       </c>
       <c r="L33" t="n">
-        <v>0.002284483249430514</v>
+        <v>0.002206897435933959</v>
       </c>
       <c r="M33" t="n">
-        <v>0.002673994019017746</v>
+        <v>0.002430157568460412</v>
       </c>
       <c r="N33" t="n">
-        <v>0.002292417869415485</v>
+        <v>0.002210381135146591</v>
       </c>
       <c r="O33" t="n">
-        <v>0.003484588480099936</v>
+        <v>0.003429116475887407</v>
       </c>
       <c r="P33" t="n">
-        <v>0.002256153882282031</v>
+        <v>0.002192134815585888</v>
       </c>
       <c r="Q33" t="n">
-        <v>0.002203059074011979</v>
+        <v>0.002157641902750693</v>
       </c>
       <c r="R33" t="n">
-        <v>0.002302463595977799</v>
+        <v>0.002213637185237937</v>
       </c>
       <c r="S33" t="n">
-        <v>0.002270072086516787</v>
+        <v>0.002200244650743168</v>
       </c>
       <c r="T33" t="n">
-        <v>0.002323509366850112</v>
+        <v>0.002227154788912327</v>
       </c>
       <c r="U33" t="n">
-        <v>0.005339712143910201</v>
+        <v>0.005234035447660113</v>
       </c>
       <c r="V33" t="n">
-        <v>0.002172411960301581</v>
+        <v>0.002141628480841093</v>
       </c>
       <c r="W33" t="n">
-        <v>0.005761048801559468</v>
+        <v>0.005628674825458549</v>
       </c>
       <c r="X33" t="n">
-        <v>0.002275668393976542</v>
+        <v>0.002199997714052457</v>
       </c>
       <c r="Y33" t="n">
-        <v>0.002279270404251617</v>
+        <v>0.002203799613898741</v>
       </c>
       <c r="Z33" t="n">
-        <v>0.004227252806225441</v>
+        <v>0.004182677669102281</v>
       </c>
       <c r="AA33" t="n">
-        <v>0.002345810466779784</v>
+        <v>0.002242974126530996</v>
       </c>
       <c r="AB33" t="n">
-        <v>0.002438954428898802</v>
+        <v>0.002290712700911078</v>
       </c>
     </row>
   </sheetData>
@@ -12230,85 +12230,85 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.002216154632333393</v>
+        <v>0.002166769853146477</v>
       </c>
       <c r="C33" t="n">
-        <v>0.002135060223851739</v>
+        <v>0.002115216917013695</v>
       </c>
       <c r="D33" t="n">
-        <v>0.002295069345367563</v>
+        <v>0.002209791748233211</v>
       </c>
       <c r="E33" t="n">
-        <v>0.002025175313998876</v>
+        <v>0.001992971768417286</v>
       </c>
       <c r="F33" t="n">
-        <v>0.002173447934440572</v>
+        <v>0.002138703661154242</v>
       </c>
       <c r="G33" t="n">
-        <v>0.00225154830352027</v>
+        <v>0.002188552258790959</v>
       </c>
       <c r="H33" t="n">
-        <v>0.002309116458460676</v>
+        <v>0.002215308270311376</v>
       </c>
       <c r="I33" t="n">
-        <v>0.002302816745987321</v>
+        <v>0.002213493592160373</v>
       </c>
       <c r="J33" t="n">
-        <v>0.002282706753565021</v>
+        <v>0.002204820175392471</v>
       </c>
       <c r="K33" t="n">
-        <v>0.00229975040739303</v>
+        <v>0.002217614034948603</v>
       </c>
       <c r="L33" t="n">
-        <v>0.002246899655547371</v>
+        <v>0.00218355558065874</v>
       </c>
       <c r="M33" t="n">
-        <v>0.002595327956597345</v>
+        <v>0.00238311720610476</v>
       </c>
       <c r="N33" t="n">
-        <v>0.002225530559531042</v>
+        <v>0.002169775824284563</v>
       </c>
       <c r="O33" t="n">
-        <v>0.003427444210659996</v>
+        <v>0.003385692855063976</v>
       </c>
       <c r="P33" t="n">
-        <v>0.002244479498116907</v>
+        <v>0.002184327484942943</v>
       </c>
       <c r="Q33" t="n">
-        <v>0.002176365634872079</v>
+        <v>0.002141139790616563</v>
       </c>
       <c r="R33" t="n">
-        <v>0.002264760430086815</v>
+        <v>0.002190727387488403</v>
       </c>
       <c r="S33" t="n">
-        <v>0.002251108633408203</v>
+        <v>0.00218793962308343</v>
       </c>
       <c r="T33" t="n">
-        <v>0.002283372002664321</v>
+        <v>0.00220251779301345</v>
       </c>
       <c r="U33" t="n">
-        <v>0.00527336734297373</v>
+        <v>0.005193296658157081</v>
       </c>
       <c r="V33" t="n">
-        <v>0.002184798944311838</v>
+        <v>0.002148488174242431</v>
       </c>
       <c r="W33" t="n">
-        <v>0.005735195209010237</v>
+        <v>0.005611623884805239</v>
       </c>
       <c r="X33" t="n">
-        <v>0.002350059382352547</v>
+        <v>0.002242749862191568</v>
       </c>
       <c r="Y33" t="n">
-        <v>0.002377315333242683</v>
+        <v>0.002260931995113221</v>
       </c>
       <c r="Z33" t="n">
-        <v>0.004218549897765358</v>
+        <v>0.004176717176435083</v>
       </c>
       <c r="AA33" t="n">
-        <v>0.002345222622968696</v>
+        <v>0.002241340195348291</v>
       </c>
       <c r="AB33" t="n">
-        <v>0.002411632447001927</v>
+        <v>0.002273636090213982</v>
       </c>
     </row>
   </sheetData>
@@ -15202,85 +15202,85 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.002189070859445308</v>
+        <v>0.002147354714274794</v>
       </c>
       <c r="C33" t="n">
-        <v>0.002070379217486682</v>
+        <v>0.002051893861649749</v>
       </c>
       <c r="D33" t="n">
-        <v>0.00221710242691513</v>
+        <v>0.002161542697568924</v>
       </c>
       <c r="E33" t="n">
-        <v>0.001997927884864302</v>
+        <v>0.001976309445999851</v>
       </c>
       <c r="F33" t="n">
-        <v>0.002176135332285777</v>
+        <v>0.002136632989472963</v>
       </c>
       <c r="G33" t="n">
-        <v>0.002224750315659626</v>
+        <v>0.002169570182186782</v>
       </c>
       <c r="H33" t="n">
-        <v>0.002283821493742583</v>
+        <v>0.002196766485652546</v>
       </c>
       <c r="I33" t="n">
-        <v>0.002270348868179306</v>
+        <v>0.002191518940185985</v>
       </c>
       <c r="J33" t="n">
-        <v>0.00226079721129203</v>
+        <v>0.002188899664081458</v>
       </c>
       <c r="K33" t="n">
-        <v>0.002325592983517409</v>
+        <v>0.002229786077514294</v>
       </c>
       <c r="L33" t="n">
-        <v>0.002217541702250368</v>
+        <v>0.00216339648440905</v>
       </c>
       <c r="M33" t="n">
-        <v>0.002493349765201255</v>
+        <v>0.002324006218942921</v>
       </c>
       <c r="N33" t="n">
-        <v>0.002177855731051739</v>
+        <v>0.002137873064462944</v>
       </c>
       <c r="O33" t="n">
-        <v>0.003408758887002905</v>
+        <v>0.00336822655240225</v>
       </c>
       <c r="P33" t="n">
-        <v>0.002217593914046866</v>
+        <v>0.002165270689324114</v>
       </c>
       <c r="Q33" t="n">
-        <v>0.00216529888988993</v>
+        <v>0.00213125539618194</v>
       </c>
       <c r="R33" t="n">
-        <v>0.002264840413381659</v>
+        <v>0.002186878833940231</v>
       </c>
       <c r="S33" t="n">
-        <v>0.002230388980812707</v>
+        <v>0.002172157188246353</v>
       </c>
       <c r="T33" t="n">
-        <v>0.002282816194006284</v>
+        <v>0.002198298527463866</v>
       </c>
       <c r="U33" t="n">
-        <v>0.005116565768928512</v>
+        <v>0.005035864126139332</v>
       </c>
       <c r="V33" t="n">
-        <v>0.00221087483408982</v>
+        <v>0.002161508399397544</v>
       </c>
       <c r="W33" t="n">
-        <v>0.005557970804465649</v>
+        <v>0.005450336560140776</v>
       </c>
       <c r="X33" t="n">
-        <v>0.002366471368212426</v>
+        <v>0.002250563829626229</v>
       </c>
       <c r="Y33" t="n">
-        <v>0.002501787779449691</v>
+        <v>0.002329448764436718</v>
       </c>
       <c r="Z33" t="n">
-        <v>0.004187063056181572</v>
+        <v>0.004153224310393398</v>
       </c>
       <c r="AA33" t="n">
-        <v>0.002341212350839962</v>
+        <v>0.002234899939279773</v>
       </c>
       <c r="AB33" t="n">
-        <v>0.002371478666863426</v>
+        <v>0.002247690036454721</v>
       </c>
     </row>
   </sheetData>
@@ -18174,85 +18174,85 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.002111586184091462</v>
+        <v>0.002095105783899537</v>
       </c>
       <c r="C33" t="n">
-        <v>0.00208182231611249</v>
+        <v>0.002074723168092073</v>
       </c>
       <c r="D33" t="n">
-        <v>0.002170268507091807</v>
+        <v>0.002128366469866226</v>
       </c>
       <c r="E33" t="n">
-        <v>0.001977364031206943</v>
+        <v>0.001957554938415147</v>
       </c>
       <c r="F33" t="n">
-        <v>0.002109490819673127</v>
+        <v>0.00209271725259504</v>
       </c>
       <c r="G33" t="n">
-        <v>0.002129384524326604</v>
+        <v>0.002106534415361579</v>
       </c>
       <c r="H33" t="n">
-        <v>0.002198967657230566</v>
+        <v>0.002143716569161084</v>
       </c>
       <c r="I33" t="n">
-        <v>0.002177230334957289</v>
+        <v>0.0021320856545072</v>
       </c>
       <c r="J33" t="n">
-        <v>0.002157264452595416</v>
+        <v>0.002122571982662949</v>
       </c>
       <c r="K33" t="n">
-        <v>0.002217746200331694</v>
+        <v>0.002159089149944044</v>
       </c>
       <c r="L33" t="n">
-        <v>0.00217438080326979</v>
+        <v>0.002134274540149135</v>
       </c>
       <c r="M33" t="n">
-        <v>0.002260755514379891</v>
+        <v>0.002184518150319245</v>
       </c>
       <c r="N33" t="n">
-        <v>0.002193343867681176</v>
+        <v>0.002143173858457574</v>
       </c>
       <c r="O33" t="n">
-        <v>0.003313040830116299</v>
+        <v>0.003292915430171067</v>
       </c>
       <c r="P33" t="n">
-        <v>0.002148856475644276</v>
+        <v>0.002117787345533955</v>
       </c>
       <c r="Q33" t="n">
-        <v>0.002145140796655047</v>
+        <v>0.002114588003572003</v>
       </c>
       <c r="R33" t="n">
-        <v>0.002177611878550321</v>
+        <v>0.002131718325300196</v>
       </c>
       <c r="S33" t="n">
-        <v>0.00214893968503106</v>
+        <v>0.002119527913910356</v>
       </c>
       <c r="T33" t="n">
-        <v>0.002148420119352717</v>
+        <v>0.002116082552686877</v>
       </c>
       <c r="U33" t="n">
-        <v>0.005158511476191509</v>
+        <v>0.005107236966954224</v>
       </c>
       <c r="V33" t="n">
-        <v>0.002112765689212953</v>
+        <v>0.002095822394084766</v>
       </c>
       <c r="W33" t="n">
-        <v>0.005656625538065642</v>
+        <v>0.005546628678669938</v>
       </c>
       <c r="X33" t="n">
-        <v>0.002184088774448292</v>
+        <v>0.002136812305851719</v>
       </c>
       <c r="Y33" t="n">
-        <v>0.00212617303722928</v>
+        <v>0.002103083580939669</v>
       </c>
       <c r="Z33" t="n">
-        <v>0.004152247288976743</v>
+        <v>0.004124076399523727</v>
       </c>
       <c r="AA33" t="n">
-        <v>0.002232027522048791</v>
+        <v>0.002165904309650273</v>
       </c>
       <c r="AB33" t="n">
-        <v>0.002241691416761634</v>
+        <v>0.002169330551277539</v>
       </c>
     </row>
   </sheetData>
@@ -21146,85 +21146,85 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.002086938836112137</v>
+        <v>0.002077119872012478</v>
       </c>
       <c r="C33" t="n">
-        <v>0.002090440258555985</v>
+        <v>0.002077585707703527</v>
       </c>
       <c r="D33" t="n">
-        <v>0.00209942784240705</v>
+        <v>0.00208412566371938</v>
       </c>
       <c r="E33" t="n">
-        <v>0.00196061862312136</v>
+        <v>0.001945080318964401</v>
       </c>
       <c r="F33" t="n">
-        <v>0.00210443872413093</v>
+        <v>0.002086950796317845</v>
       </c>
       <c r="G33" t="n">
-        <v>0.002106465227477236</v>
+        <v>0.00208962361261212</v>
       </c>
       <c r="H33" t="n">
-        <v>0.002138702412485479</v>
+        <v>0.002106208123116708</v>
       </c>
       <c r="I33" t="n">
-        <v>0.002130776252889264</v>
+        <v>0.002102355884234066</v>
       </c>
       <c r="J33" t="n">
-        <v>0.002116680421793103</v>
+        <v>0.0020953047035995</v>
       </c>
       <c r="K33" t="n">
-        <v>0.002106402475975809</v>
+        <v>0.002088686116010374</v>
       </c>
       <c r="L33" t="n">
-        <v>0.002101707179973356</v>
+        <v>0.002086663416115899</v>
       </c>
       <c r="M33" t="n">
-        <v>0.002091433892197166</v>
+        <v>0.002079397361749649</v>
       </c>
       <c r="N33" t="n">
-        <v>0.002119665047471466</v>
+        <v>0.00209651655995842</v>
       </c>
       <c r="O33" t="n">
-        <v>0.003292320026230065</v>
+        <v>0.003272029512646797</v>
       </c>
       <c r="P33" t="n">
-        <v>0.002106598499563389</v>
+        <v>0.002089259695712635</v>
       </c>
       <c r="Q33" t="n">
-        <v>0.002089898098773202</v>
+        <v>0.002078851674072647</v>
       </c>
       <c r="R33" t="n">
-        <v>0.002128751827162583</v>
+        <v>0.002100844437459391</v>
       </c>
       <c r="S33" t="n">
-        <v>0.00211683992710349</v>
+        <v>0.00209632724032061</v>
       </c>
       <c r="T33" t="n">
-        <v>0.002102965006379617</v>
+        <v>0.0020862446337294</v>
       </c>
       <c r="U33" t="n">
-        <v>0.005037497432882126</v>
+        <v>0.005027817191238861</v>
       </c>
       <c r="V33" t="n">
-        <v>0.002113170598748655</v>
+        <v>0.00209354255630831</v>
       </c>
       <c r="W33" t="n">
-        <v>0.005545436019877668</v>
+        <v>0.005475713133114025</v>
       </c>
       <c r="X33" t="n">
-        <v>0.002244371947564469</v>
+        <v>0.00217167761850682</v>
       </c>
       <c r="Y33" t="n">
-        <v>0.002136639412350279</v>
+        <v>0.002106257325829647</v>
       </c>
       <c r="Z33" t="n">
-        <v>0.004131951120553504</v>
+        <v>0.004107252834902881</v>
       </c>
       <c r="AA33" t="n">
-        <v>0.002183640036597305</v>
+        <v>0.002134234365706182</v>
       </c>
       <c r="AB33" t="n">
-        <v>0.00207796657871463</v>
+        <v>0.002071155252425022</v>
       </c>
     </row>
   </sheetData>
@@ -24118,85 +24118,85 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.002086573309556347</v>
+        <v>0.002073269722978413</v>
       </c>
       <c r="C33" t="n">
-        <v>0.002028592303839254</v>
+        <v>0.002015991775684767</v>
       </c>
       <c r="D33" t="n">
-        <v>0.002093622954455631</v>
+        <v>0.002076756789034794</v>
       </c>
       <c r="E33" t="n">
-        <v>0.001967918012497408</v>
+        <v>0.001949355346440932</v>
       </c>
       <c r="F33" t="n">
-        <v>0.002090190352499552</v>
+        <v>0.002074499506307789</v>
       </c>
       <c r="G33" t="n">
-        <v>0.002086481370851666</v>
+        <v>0.002073301023674904</v>
       </c>
       <c r="H33" t="n">
-        <v>0.002107848494881253</v>
+        <v>0.002084465579743834</v>
       </c>
       <c r="I33" t="n">
-        <v>0.002095633366350474</v>
+        <v>0.002077685341483746</v>
       </c>
       <c r="J33" t="n">
-        <v>0.002101311401960826</v>
+        <v>0.002081987170085191</v>
       </c>
       <c r="K33" t="n">
-        <v>0.002085066415743493</v>
+        <v>0.002071808217054663</v>
       </c>
       <c r="L33" t="n">
-        <v>0.002093840978828057</v>
+        <v>0.002077915174296099</v>
       </c>
       <c r="M33" t="n">
-        <v>0.002083930019689476</v>
+        <v>0.002070925269547671</v>
       </c>
       <c r="N33" t="n">
-        <v>0.002096462542592787</v>
+        <v>0.002078616908544994</v>
       </c>
       <c r="O33" t="n">
-        <v>0.003313876956635143</v>
+        <v>0.003283066846571472</v>
       </c>
       <c r="P33" t="n">
-        <v>0.002102356427045528</v>
+        <v>0.002083215789094349</v>
       </c>
       <c r="Q33" t="n">
-        <v>0.002079916200110424</v>
+        <v>0.002068874606836341</v>
       </c>
       <c r="R33" t="n">
-        <v>0.002119134273127036</v>
+        <v>0.002091152416584395</v>
       </c>
       <c r="S33" t="n">
-        <v>0.002100299114840013</v>
+        <v>0.002081886867926438</v>
       </c>
       <c r="T33" t="n">
-        <v>0.00208573079052912</v>
+        <v>0.00207198914471683</v>
       </c>
       <c r="U33" t="n">
-        <v>0.004879309227244545</v>
+        <v>0.004867909266182231</v>
       </c>
       <c r="V33" t="n">
-        <v>0.002111564517622179</v>
+        <v>0.002088775741453347</v>
       </c>
       <c r="W33" t="n">
-        <v>0.005375757521699713</v>
+        <v>0.00531799666322109</v>
       </c>
       <c r="X33" t="n">
-        <v>0.002273062537062237</v>
+        <v>0.002185943854179736</v>
       </c>
       <c r="Y33" t="n">
-        <v>0.002120016458382192</v>
+        <v>0.002092388134277047</v>
       </c>
       <c r="Z33" t="n">
-        <v>0.004103612870672723</v>
+        <v>0.004084790385541162</v>
       </c>
       <c r="AA33" t="n">
-        <v>0.002181413933452052</v>
+        <v>0.00212896388804976</v>
       </c>
       <c r="AB33" t="n">
-        <v>0.002080860693406894</v>
+        <v>0.002068855841269872</v>
       </c>
     </row>
   </sheetData>
@@ -27090,85 +27090,85 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.002192777787055673</v>
+        <v>0.002151351380811987</v>
       </c>
       <c r="C33" t="n">
-        <v>0.002113110945346263</v>
+        <v>0.002099817516538958</v>
       </c>
       <c r="D33" t="n">
-        <v>0.002225120023426505</v>
+        <v>0.002166888797949706</v>
       </c>
       <c r="E33" t="n">
-        <v>0.002001136371537</v>
+        <v>0.001977276006584194</v>
       </c>
       <c r="F33" t="n">
-        <v>0.002157924381717813</v>
+        <v>0.002127825992097599</v>
       </c>
       <c r="G33" t="n">
-        <v>0.002248649739736887</v>
+        <v>0.002186051692641883</v>
       </c>
       <c r="H33" t="n">
-        <v>0.002309714776430893</v>
+        <v>0.002214238378412354</v>
       </c>
       <c r="I33" t="n">
-        <v>0.002259611212475037</v>
+        <v>0.002186926608279361</v>
       </c>
       <c r="J33" t="n">
-        <v>0.002263803782205028</v>
+        <v>0.002193272908537871</v>
       </c>
       <c r="K33" t="n">
-        <v>0.002315088217363544</v>
+        <v>0.002224883693086527</v>
       </c>
       <c r="L33" t="n">
-        <v>0.002257492531790681</v>
+        <v>0.002189261526611697</v>
       </c>
       <c r="M33" t="n">
-        <v>0.002629419653595992</v>
+        <v>0.002411396579113016</v>
       </c>
       <c r="N33" t="n">
-        <v>0.002304438962409954</v>
+        <v>0.002214625446347259</v>
       </c>
       <c r="O33" t="n">
-        <v>0.003417295471811313</v>
+        <v>0.003376374596751147</v>
       </c>
       <c r="P33" t="n">
-        <v>0.002226302732398908</v>
+        <v>0.002171253936808622</v>
       </c>
       <c r="Q33" t="n">
-        <v>0.002182248330597441</v>
+        <v>0.002142976195059259</v>
       </c>
       <c r="R33" t="n">
-        <v>0.002265041724063618</v>
+        <v>0.002189094521203938</v>
       </c>
       <c r="S33" t="n">
-        <v>0.002213318920307605</v>
+        <v>0.002164719032007423</v>
       </c>
       <c r="T33" t="n">
-        <v>0.002256206622140849</v>
+        <v>0.002185057587120688</v>
       </c>
       <c r="U33" t="n">
-        <v>0.005265181516349738</v>
+        <v>0.005180445925756743</v>
       </c>
       <c r="V33" t="n">
-        <v>0.002157734773494152</v>
+        <v>0.002129919522382514</v>
       </c>
       <c r="W33" t="n">
-        <v>0.005667238401258791</v>
+        <v>0.005562671873826435</v>
       </c>
       <c r="X33" t="n">
-        <v>0.002306223213174945</v>
+        <v>0.00221505773322728</v>
       </c>
       <c r="Y33" t="n">
-        <v>0.002253695800092286</v>
+        <v>0.002185830844669379</v>
       </c>
       <c r="Z33" t="n">
-        <v>0.004209821303628227</v>
+        <v>0.004167960045155368</v>
       </c>
       <c r="AA33" t="n">
-        <v>0.002317335429114105</v>
+        <v>0.002223281578712134</v>
       </c>
       <c r="AB33" t="n">
-        <v>0.002386221534025378</v>
+        <v>0.002257808284975092</v>
       </c>
     </row>
   </sheetData>
@@ -30062,85 +30062,85 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.002091835903558035</v>
+        <v>0.002084237793398203</v>
       </c>
       <c r="C33" t="n">
-        <v>0.002100323907039155</v>
+        <v>0.002087899833557652</v>
       </c>
       <c r="D33" t="n">
-        <v>0.002118577278765304</v>
+        <v>0.002099606058951044</v>
       </c>
       <c r="E33" t="n">
-        <v>0.001968664081062092</v>
+        <v>0.001953396311923133</v>
       </c>
       <c r="F33" t="n">
-        <v>0.002105849359130781</v>
+        <v>0.002092047908240222</v>
       </c>
       <c r="G33" t="n">
-        <v>0.002216785614862926</v>
+        <v>0.002162580987366551</v>
       </c>
       <c r="H33" t="n">
-        <v>0.00222229642281156</v>
+        <v>0.002158264282195793</v>
       </c>
       <c r="I33" t="n">
-        <v>0.002131341396275122</v>
+        <v>0.002106759984715577</v>
       </c>
       <c r="J33" t="n">
-        <v>0.00217256079500832</v>
+        <v>0.002133469844373325</v>
       </c>
       <c r="K33" t="n">
-        <v>0.002167416278062234</v>
+        <v>0.002130338918730012</v>
       </c>
       <c r="L33" t="n">
-        <v>0.002166009157964709</v>
+        <v>0.002129879291635118</v>
       </c>
       <c r="M33" t="n">
-        <v>0.002142311748141464</v>
+        <v>0.002114189543766206</v>
       </c>
       <c r="N33" t="n">
-        <v>0.002141868489165529</v>
+        <v>0.002113409935494228</v>
       </c>
       <c r="O33" t="n">
-        <v>0.003301775174812474</v>
+        <v>0.003286232667685455</v>
       </c>
       <c r="P33" t="n">
-        <v>0.002174489582602542</v>
+        <v>0.002135091172917857</v>
       </c>
       <c r="Q33" t="n">
-        <v>0.002125908692591486</v>
+        <v>0.00210484909711103</v>
       </c>
       <c r="R33" t="n">
-        <v>0.002163907465169184</v>
+        <v>0.002125351827568559</v>
       </c>
       <c r="S33" t="n">
-        <v>0.00213554345939219</v>
+        <v>0.002111501003629839</v>
       </c>
       <c r="T33" t="n">
-        <v>0.002135986540659981</v>
+        <v>0.002109670320117591</v>
       </c>
       <c r="U33" t="n">
-        <v>0.005085508169701431</v>
+        <v>0.00506600698632384</v>
       </c>
       <c r="V33" t="n">
-        <v>0.002128263138451187</v>
+        <v>0.002106840098302914</v>
       </c>
       <c r="W33" t="n">
-        <v>0.005615118328053257</v>
+        <v>0.00552493822688825</v>
       </c>
       <c r="X33" t="n">
-        <v>0.002295341613189393</v>
+        <v>0.002204863428812837</v>
       </c>
       <c r="Y33" t="n">
-        <v>0.002322700259838147</v>
+        <v>0.002221607758515279</v>
       </c>
       <c r="Z33" t="n">
-        <v>0.004132789193516353</v>
+        <v>0.004111558652688934</v>
       </c>
       <c r="AA33" t="n">
-        <v>0.002189362616243367</v>
+        <v>0.002141875885265088</v>
       </c>
       <c r="AB33" t="n">
-        <v>0.002732286758224187</v>
+        <v>0.002453960859190759</v>
       </c>
     </row>
   </sheetData>
